--- a/results/3er_crimelaw.xlsx
+++ b/results/3er_crimelaw.xlsx
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D2" t="n">
-        <v>15.68627450980392</v>
+        <v>20.60301507537688</v>
       </c>
     </row>
     <row r="3">
@@ -461,13 +461,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="C3" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>35.44303797468354</v>
+        <v>32.18390804597701</v>
       </c>
     </row>
     <row r="4">
